--- a/DE190094_NguyenVanQuang_AI_AuditLog.xlsx
+++ b/DE190094_NguyenVanQuang_AI_AuditLog.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9048" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9048" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="190">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -174,76 +174,10 @@
     <t>001</t>
   </si>
   <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
-    <t>PROBLEM-SOLVING</t>
-  </si>
-  <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
     <t>003</t>
-  </si>
-  <si>
-    <t>VERIFICATION</t>
-  </si>
-  <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -834,6 +768,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -849,9 +786,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,14 +1100,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1185,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1193,7 +1127,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1201,7 +1135,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1209,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1271,7 +1205,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>19</v>
@@ -1389,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1403,28 +1337,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1452,343 +1386,295 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+    <row r="4" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="B4" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+      <c r="B5" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>70</v>
+      <c r="B6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="18">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D7" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="E7" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="F7" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="G7" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="H7" s="18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="C8" s="18" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
-        <v>5</v>
-      </c>
-      <c r="B8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="F8" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="G8" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="H8" s="18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="C9" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="D9" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="18">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="18" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
-        <v>6</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="H9" s="24" t="s">
+    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
-        <v>7</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="24" t="s">
+      <c r="C13" s="18" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
-        <v>8</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="H11" s="24" t="s">
+      <c r="D13" s="18" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
-        <v>9</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="24" t="s">
+      <c r="E13" s="18" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
-        <v>10</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="H13" s="24" t="s">
+      <c r="F13" s="18" t="s">
         <v>187</v>
       </c>
+      <c r="G13" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>194</v>
-      </c>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>201</v>
-      </c>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>208</v>
-      </c>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
@@ -1849,36 +1735,6 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1900,63 +1756,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2123,73 +1979,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2213,202 +2069,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -2416,13 +2272,13 @@
         <v>41</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2435,7 +2291,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2443,7 +2299,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
